--- a/InputData/elec/WUbPPT/Water Use by Power Plant Type.xlsx
+++ b/InputData/elec/WUbPPT/Water Use by Power Plant Type.xlsx
@@ -2551,7 +2551,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4985D2B5-6EB6-4647-8B50-F2B10163C166}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6CB23184-7976-4D49-8671-E4DE57E06C98}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
